--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484376_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484376_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8886</v>
+        <v>9.8599</v>
       </c>
       <c r="E2" t="n">
-        <v>8.020300000000001</v>
+        <v>7.4742</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8683</v>
+        <v>2.3857</v>
       </c>
       <c r="G2" t="n">
         <v>4.1504</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2461</v>
+        <v>0.2174</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3798</v>
+        <v>-0.1663</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1338</v>
+        <v>0.3837</v>
       </c>
       <c r="V2" t="n">
         <v>4.3201</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8881</v>
+        <v>3.8554</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8066</v>
+        <v>3.5638</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0815</v>
+        <v>0.2916</v>
       </c>
       <c r="G3" t="n">
         <v>2.3759</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3634</v>
+        <v>0.3308</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1515</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2119</v>
+        <v>0.4221</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6093</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7509</v>
+        <v>3.4223</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5894</v>
+        <v>0.7511</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1615</v>
+        <v>2.6712</v>
       </c>
       <c r="G4" t="n">
         <v>0.8401999999999999</v>
@@ -766,13 +766,13 @@
         <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>0.8714</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4483</v>
+        <v>-0.2866</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6483</v>
+        <v>1.1581</v>
       </c>
       <c r="V4" t="n">
         <v>2.4921</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.731</v>
+        <v>0.1515</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7222</v>
+        <v>0.1155</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.036</v>
       </c>
       <c r="G5" t="n">
         <v>4.1135</v>
@@ -844,13 +844,13 @@
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9811</v>
+        <v>0.4016</v>
       </c>
       <c r="T5" t="n">
-        <v>0.831</v>
+        <v>0.2244</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1501</v>
+        <v>0.1773</v>
       </c>
       <c r="V5" t="n">
         <v>-2.2149</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5761</v>
+        <v>-0.9552</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7873</v>
+        <v>0.866</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9043</v>
+        <v>1.2848</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4838</v>
+        <v>-0.9537</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3881</v>
+        <v>2.2384</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0686</v>
+        <v>1.6633</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3543</v>
+        <v>0.3684</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7144</v>
+        <v>1.2949</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1643</v>
+        <v>-0.3785</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.838</v>
+        <v>-1.3221</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6737</v>
+        <v>0.9435</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1022</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2371</v>
+        <v>-0.866</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8198</v>
+        <v>-0.4697</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0569</v>
+        <v>-0.3963</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8827</v>
+        <v>-0.5417</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2585</v>
+        <v>-2.1111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3758</v>
+        <v>1.5694</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2848</v>
+        <v>1.9043</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9537</v>
+        <v>-0.4838</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2384</v>
+        <v>2.3881</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6633</v>
+        <v>2.0686</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3684</v>
+        <v>0.3543</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2949</v>
+        <v>1.7144</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3785</v>
+        <v>-0.1643</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3221</v>
+        <v>-0.838</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9435</v>
+        <v>0.6737</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>-4.1022</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6596</v>
+        <v>0.4842</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.773</v>
+        <v>-0.3548</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8866000000000001</v>
+        <v>0.839</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7495</v>
+        <v>-1.5605</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4052</v>
+        <v>-0.524</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3444</v>
+        <v>-1.0365</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3546</v>
+        <v>-0.4471</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5145</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1599</v>
+        <v>-0.364</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06950000000000001</v>
+        <v>-0.5722</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5513</v>
+        <v>0.0614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6208</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4241</v>
+        <v>0.1251</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.1445</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5391</v>
+        <v>0.2696</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8089</v>
+        <v>0.1871</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3026</v>
+        <v>0.0482</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5063</v>
+        <v>0.1389</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0079</v>
+        <v>-1.6484</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-1.3041</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2816</v>
+        <v>-0.3444</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4471</v>
+        <v>-0.3546</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-1.5145</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.364</v>
+        <v>1.1599</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5722</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0614</v>
+        <v>-0.5513</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.6208</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1251</v>
+        <v>-0.4241</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1445</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2696</v>
+        <v>0.5391</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2602</v>
+        <v>-0.7078</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.154</v>
+        <v>-0.2015</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1062</v>
+        <v>-0.5063</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0295</v>
+        <v>-2.3467</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0317</v>
+        <v>-1.5667</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9978</v>
+        <v>-0.7799</v>
       </c>
       <c r="G10" t="n">
         <v>0.6652</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8082</v>
+        <v>-1.1253</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.271</v>
+        <v>-0.806</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5372</v>
+        <v>-0.3193</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4959</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10.8002</v>
+        <v>11.1027</v>
       </c>
       <c r="E11" t="n">
-        <v>5.140700000000001</v>
+        <v>5.4435</v>
       </c>
       <c r="F11" t="n">
-        <v>5.6594</v>
+        <v>5.659099999999999</v>
       </c>
       <c r="G11" t="n">
         <v>14.5326</v>
@@ -1312,13 +1312,13 @@
         <v>10.7438</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5092000000000005</v>
+        <v>-0.2065999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.4064</v>
+        <v>-2.1036</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8971</v>
+        <v>1.8972</v>
       </c>
       <c r="V11" t="n">
         <v>1.6604</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.0583</v>
+        <v>3.5048</v>
       </c>
       <c r="E12" t="n">
-        <v>5.111</v>
+        <v>4.5043</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0527</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>2.0948</v>
@@ -1390,13 +1390,13 @@
         <v>2.3441</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1589</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5835</v>
+        <v>-0.0232</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5754</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.6093</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3177</v>
+        <v>2.8666</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4471</v>
+        <v>1.9415</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8706</v>
+        <v>0.9251</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4732</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2635</v>
+        <v>0.8124</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2272</v>
+        <v>0.7216</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.5507</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5072</v>
+        <v>1.7118</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1928</v>
+        <v>-0.6872</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.3991</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9601</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8264</v>
+        <v>1.0311</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5226</v>
+        <v>-0.017</v>
       </c>
       <c r="U14" t="n">
-        <v>1.349</v>
+        <v>1.0481</v>
       </c>
       <c r="V14" t="n">
         <v>0.6642</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.915</v>
+        <v>-1.4405</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7936</v>
+        <v>-0.5913</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1215</v>
+        <v>-0.8491</v>
       </c>
       <c r="G15" t="n">
         <v>-2.6072</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0659</v>
+        <v>0.4086</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0384</v>
+        <v>0.1638</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0275</v>
+        <v>0.2448</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6093</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0542</v>
+        <v>-1.8339</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3325</v>
+        <v>-1.0292</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7216</v>
+        <v>-0.8047</v>
       </c>
       <c r="G16" t="n">
         <v>0.0114</v>
@@ -1702,13 +1702,13 @@
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0655</v>
+        <v>0.1548</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4237</v>
+        <v>-0.1203</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3581</v>
+        <v>0.2751</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2186</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1115</v>
+        <v>-2.3604</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3476</v>
+        <v>-1.6509</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7639</v>
+        <v>-0.7094</v>
       </c>
       <c r="G17" t="n">
         <v>-2.5055</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.394</v>
+        <v>0.1452</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3247</v>
+        <v>0.0214</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0693</v>
+        <v>0.1238</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1603</v>
+        <v>-2.4065</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8767</v>
+        <v>-1.4945</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2836</v>
+        <v>-0.912</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.9145</v>
+        <v>-1.809</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2758</v>
+        <v>-1.2149</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.6388</v>
+        <v>-0.5942</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5081</v>
+        <v>0.3879</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4556</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.9637</v>
+        <v>0.0809</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4065</v>
+        <v>-2.1969</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7314</v>
+        <v>-1.5219</v>
       </c>
       <c r="O18" t="n">
         <v>-0.6751</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
         <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9811</v>
+        <v>-0.6328</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2116</v>
+        <v>-0.9876</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1927</v>
+        <v>0.3548</v>
       </c>
       <c r="V18" t="n">
-        <v>1.7731</v>
+        <v>-0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>2.9917</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
         <v>-1.2186</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2985</v>
+        <v>-2.6104</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8989</v>
+        <v>-2.079</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3995</v>
+        <v>-0.5314</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.809</v>
+        <v>-4.9145</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2149</v>
+        <v>-0.2758</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5942</v>
+        <v>-4.6388</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3879</v>
+        <v>-2.5081</v>
       </c>
       <c r="K19" t="n">
-        <v>0.307</v>
+        <v>1.4556</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>-3.9637</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1969</v>
+        <v>-2.4065</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5219</v>
+        <v>-1.7314</v>
       </c>
       <c r="O19" t="n">
         <v>-0.6751</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R19" t="n">
         <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5248</v>
+        <v>0.531</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.392</v>
+        <v>-0.4138</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1327</v>
+        <v>0.9449</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9414</v>
+        <v>1.7731</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>2.9917</v>
       </c>
       <c r="X19" t="n">
         <v>-1.2186</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8398</v>
+        <v>-3.2083</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0329</v>
+        <v>-3.1341</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8068</v>
+        <v>-0.0742</v>
       </c>
       <c r="G20" t="n">
         <v>-2.061</v>
@@ -2014,13 +2014,13 @@
         <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1109</v>
+        <v>-0.4794</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4758</v>
+        <v>-0.5769</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6351</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2772</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3041</v>
+        <v>-3.6753</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7423</v>
+        <v>-1.4389</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5618</v>
+        <v>-2.2363</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3081</v>
@@ -2092,13 +2092,13 @@
         <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3476</v>
+        <v>-0.7188</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9684</v>
+        <v>-0.665</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3792</v>
+        <v>-0.0537</v>
       </c>
       <c r="V21" t="n">
         <v>-3.2111</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.8002</v>
+        <v>-9.4521</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6592</v>
+        <v>-5.659300000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.1408</v>
+        <v>-3.7924</v>
       </c>
       <c r="G22" t="n">
         <v>-14.5324</v>
@@ -2170,13 +2170,13 @@
         <v>15.6275</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5092000000000003</v>
+        <v>1.8574</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.8971</v>
+        <v>-1.897</v>
       </c>
       <c r="U22" t="n">
-        <v>2.4063</v>
+        <v>3.7547</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6603</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484376_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484376_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1515</v>
+        <v>2.1349</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1155</v>
+        <v>2.1349</v>
       </c>
       <c r="F5" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1135</v>
+        <v>2.1349</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7632</v>
+        <v>0.921</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3504</v>
+        <v>1.214</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0129</v>
+        <v>2.1349</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6061</v>
+        <v>0.921</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1006</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8429</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4016</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2244</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1773</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.2149</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0891</v>
+        <v>0.1515</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9552</v>
+        <v>0.1155</v>
       </c>
       <c r="F6" t="n">
-        <v>0.866</v>
+        <v>0.036</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2848</v>
+        <v>4.1135</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9537</v>
+        <v>3.7632</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2384</v>
+        <v>0.3504</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6633</v>
+        <v>4.0129</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3684</v>
+        <v>4.6061</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2949</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3785</v>
+        <v>0.1006</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3221</v>
+        <v>-0.8429</v>
       </c>
       <c r="O6" t="n">
         <v>0.9435</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R6" t="n">
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.866</v>
+        <v>0.4016</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4697</v>
+        <v>0.2244</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3963</v>
+        <v>0.1773</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6642</v>
+        <v>-2.2149</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +985,72 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5417</v>
+        <v>-0.0891</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1111</v>
+        <v>-0.9552</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5694</v>
+        <v>0.866</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9043</v>
+        <v>1.2848</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4838</v>
+        <v>-0.9537</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3881</v>
+        <v>2.2384</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0686</v>
+        <v>1.6633</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3543</v>
+        <v>0.3684</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7144</v>
+        <v>1.2949</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1643</v>
+        <v>-0.3785</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.838</v>
+        <v>-1.3221</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6737</v>
+        <v>0.9435</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.1022</v>
+        <v>-2.1488</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4842</v>
+        <v>-0.866</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3548</v>
+        <v>-0.4697</v>
       </c>
       <c r="U7" t="n">
-        <v>0.839</v>
+        <v>-0.3963</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1172,6 +1212,11 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,146 +1317,152 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>11.1027</v>
+        <v>-2.6766</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4435</v>
+        <v>-4.246</v>
       </c>
       <c r="F11" t="n">
-        <v>5.659099999999999</v>
+        <v>1.5694</v>
       </c>
       <c r="G11" t="n">
-        <v>14.5326</v>
+        <v>-0.2306</v>
       </c>
       <c r="H11" t="n">
-        <v>4.418000000000002</v>
+        <v>-1.4047</v>
       </c>
       <c r="I11" t="n">
-        <v>10.1145</v>
+        <v>1.1741</v>
       </c>
       <c r="J11" t="n">
-        <v>17.5232</v>
+        <v>-0.0663</v>
       </c>
       <c r="K11" t="n">
-        <v>14.1469</v>
+        <v>-0.5667</v>
       </c>
       <c r="L11" t="n">
-        <v>3.3765</v>
+        <v>0.5004</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9907</v>
+        <v>-0.1643</v>
       </c>
       <c r="N11" t="n">
-        <v>-9.7287</v>
+        <v>-0.838</v>
       </c>
       <c r="O11" t="n">
-        <v>6.737900000000001</v>
+        <v>0.6737</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.883599999999999</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q11" t="n">
-        <v>-15.6275</v>
+        <v>-4.1022</v>
       </c>
       <c r="R11" t="n">
-        <v>10.7438</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2065999999999999</v>
+        <v>0.4842</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.1036</v>
+        <v>-0.3548</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8972</v>
+        <v>0.839</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6604</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>5.6513</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.9909</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5048</v>
+        <v>11.1027</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5043</v>
+        <v>5.443499999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9995000000000001</v>
+        <v>5.659099999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>2.0948</v>
+        <v>14.5326</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9734</v>
+        <v>4.418100000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1214</v>
+        <v>10.1145</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1804</v>
+        <v>17.5232</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9792</v>
+        <v>14.1469</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2011</v>
+        <v>3.3765</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0856</v>
+        <v>-2.9907</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0059</v>
+        <v>-9.728699999999998</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0797</v>
+        <v>6.737900000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>-4.883599999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1488</v>
+        <v>-15.6275</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3441</v>
+        <v>10.7438</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.2065999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0232</v>
+        <v>-2.1036</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6284999999999999</v>
+        <v>1.8972</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6093</v>
+        <v>1.6604</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4959</v>
+        <v>5.6513</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8865</v>
-      </c>
+        <v>-3.9909</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,11 +1541,16 @@
       <c r="X13" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7118</v>
+        <v>1.9838</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6872</v>
+        <v>2.9834</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3991</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9601</v>
+        <v>0.5738</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7718</v>
+        <v>1.6664</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1883</v>
+        <v>-1.0926</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5018</v>
+        <v>3.6594</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2292</v>
+        <v>3.6723</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7274</v>
+        <v>-0.0128</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4619</v>
+        <v>-3.0856</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.001</v>
+        <v>-2.0059</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5391</v>
+        <v>-1.0797</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0311</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.017</v>
+        <v>-0.0232</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0481</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6642</v>
+        <v>0.6093</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.4405</v>
+        <v>1.7118</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5913</v>
+        <v>-0.6872</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8491</v>
+        <v>2.3991</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.6072</v>
+        <v>-0.9601</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3776</v>
+        <v>-0.7718</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2296</v>
+        <v>-0.1883</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7552</v>
+        <v>0.5018</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7956</v>
+        <v>1.2292</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>-0.7274</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.852</v>
+        <v>-1.4619</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.582</v>
+        <v>-2.001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.27</v>
+        <v>0.5391</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4086</v>
+        <v>1.0311</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1638</v>
+        <v>-0.017</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2448</v>
+        <v>1.0481</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8339</v>
+        <v>1.521</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0292</v>
+        <v>1.521</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8047</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0114</v>
+        <v>1.521</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5104</v>
+        <v>0.307</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.499</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0446</v>
+        <v>1.521</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6782</v>
+        <v>0.307</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0332</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1678</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1346</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1548</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1203</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2751</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1811,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3604</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6509</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7094</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5055</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2763</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2292</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6723</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0387</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2377</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4045</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,13 +1856,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1452</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0214</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4065</v>
+        <v>-1.7474</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4945</v>
+        <v>-0.8983</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.912</v>
+        <v>-0.8491</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.809</v>
+        <v>-2.9142</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2149</v>
+        <v>-2.6846</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5942</v>
+        <v>-0.2296</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3879</v>
+        <v>-1.0621</v>
       </c>
       <c r="K18" t="n">
-        <v>0.307</v>
+        <v>-1.1026</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1969</v>
+        <v>-1.852</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5219</v>
+        <v>-1.582</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6751</v>
+        <v>-0.27</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6328</v>
+        <v>0.4086</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9876</v>
+        <v>0.1638</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3548</v>
+        <v>0.2448</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9414</v>
+        <v>-0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6104</v>
+        <v>-1.8339</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.079</v>
+        <v>-1.0292</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5314</v>
+        <v>-0.8047</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.9145</v>
+        <v>0.0114</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2758</v>
+        <v>0.5104</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.6388</v>
+        <v>-0.499</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5081</v>
+        <v>1.0446</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4556</v>
+        <v>1.6782</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.9637</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4065</v>
+        <v>-1.0332</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7314</v>
+        <v>-1.1678</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6751</v>
+        <v>0.1346</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.531</v>
+        <v>0.1548</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4138</v>
+        <v>-0.1203</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9449</v>
+        <v>0.2751</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7731</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>2.9917</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2083</v>
+        <v>-2.3604</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1341</v>
+        <v>-1.6509</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0742</v>
+        <v>-0.7094</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.061</v>
+        <v>-2.5055</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9954</v>
+        <v>-2.2763</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0655</v>
+        <v>-0.2292</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4083</v>
+        <v>-1.6723</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2519</v>
+        <v>-1.0387</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6603</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6526</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2474</v>
+        <v>-1.2377</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4052</v>
+        <v>0.4045</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4794</v>
+        <v>0.1452</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5769</v>
+        <v>0.0214</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.1238</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6753</v>
+        <v>-2.4065</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4389</v>
+        <v>-1.4945</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2363</v>
+        <v>-0.912</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3081</v>
+        <v>-1.809</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0786</v>
+        <v>-1.2149</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3867</v>
+        <v>-0.5942</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2186</v>
+        <v>0.3879</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6605</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.442</v>
+        <v>0.0809</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5267</v>
+        <v>-2.1969</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.582</v>
+        <v>-1.5219</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9447</v>
+        <v>-0.6751</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7188</v>
+        <v>-0.6328</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.665</v>
+        <v>-0.9876</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0537</v>
+        <v>0.3548</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.2111</v>
+        <v>-0.9414</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.9925</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,318 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.4521</v>
+        <v>-2.6104</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.659300000000001</v>
+        <v>-2.079</v>
       </c>
       <c r="F22" t="n">
+        <v>-0.5314</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-4.9145</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.2758</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-4.6388</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-2.5081</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.4556</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-3.9637</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-2.4065</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.7314</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.6751</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.4138</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.7731</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.9917</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B. MORALES CONILL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-3.2083</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.1341</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.0742</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.061</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.9954</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.0655</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.4083</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.6603</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.6526</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.2474</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.4052</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.4794</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.5769</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>G. PEREZ LAYUNTA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.6753</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.4389</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.2363</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.3081</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.0786</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.3867</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.6605</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.442</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.5267</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.582</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.9447</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.7188</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.665</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.0537</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-3.2111</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-1.9925</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484376_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-9.451999999999998</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.6592</v>
+      </c>
+      <c r="F25" t="n">
         <v>-3.7924</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G25" t="n">
         <v>-14.5324</v>
       </c>
-      <c r="H22" t="n">
-        <v>-4.418</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="H25" t="n">
+        <v>-4.418000000000001</v>
+      </c>
+      <c r="I25" t="n">
         <v>-10.1146</v>
       </c>
-      <c r="J22" t="n">
-        <v>2.990699999999999</v>
-      </c>
-      <c r="K22" t="n">
-        <v>9.7286</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-6.7381</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="J25" t="n">
+        <v>2.990800000000001</v>
+      </c>
+      <c r="K25" t="n">
+        <v>9.7287</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-6.738</v>
+      </c>
+      <c r="M25" t="n">
         <v>-17.5231</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N25" t="n">
         <v>-14.1469</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O25" t="n">
         <v>-3.376300000000001</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P25" t="n">
         <v>4.8834</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q25" t="n">
         <v>-10.744</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R25" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S25" t="n">
         <v>1.8574</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>-1.897</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U25" t="n">
         <v>3.7547</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V25" t="n">
         <v>-1.6603</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W25" t="n">
         <v>3.9909</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X25" t="n">
         <v>-5.6511</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
